--- a/Qualité insuffisante des lieux de baignade.xlsx
+++ b/Qualité insuffisante des lieux de baignade.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehl\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oxfamfrance-my.sharepoint.com/personal/rehl_oxfamfrance_org/Documents/Documents/Santé et climat/Données/Baignade/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ED6184-30A3-4159-AD47-531517E65389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C8976A-2C29-4FDD-95C1-99C4A4A2527E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="3705" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lieux de baignade" sheetId="3" r:id="rId1"/>
+    <sheet name="Lieux de baignade - MAJ 2023" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>Puy-de-Dôme</t>
   </si>
@@ -85,18 +85,12 @@
     <t>Aisne</t>
   </si>
   <si>
-    <t>UCCIANI</t>
-  </si>
-  <si>
     <t>Indre</t>
   </si>
   <si>
     <t>Indre-et-Loire</t>
   </si>
   <si>
-    <t>Guadeloupe</t>
-  </si>
-  <si>
     <t>Alpes-Maritimes</t>
   </si>
   <si>
@@ -118,9 +112,6 @@
     <t>Dordogne</t>
   </si>
   <si>
-    <t>Guyane</t>
-  </si>
-  <si>
     <t>Paris</t>
   </si>
   <si>
@@ -137,13 +128,208 @@
   </si>
   <si>
     <t>Taux de pauvreté</t>
+  </si>
+  <si>
+    <t>Ain</t>
+  </si>
+  <si>
+    <t>Alpes-de-Haute-Provence</t>
+  </si>
+  <si>
+    <t>Hautes-Alpes</t>
+  </si>
+  <si>
+    <t>Ardennes</t>
+  </si>
+  <si>
+    <t>Ariège</t>
+  </si>
+  <si>
+    <t>Aube</t>
+  </si>
+  <si>
+    <t>Bouches-du-Rhône</t>
+  </si>
+  <si>
+    <t>Calvados</t>
+  </si>
+  <si>
+    <t>Cantal</t>
+  </si>
+  <si>
+    <t>Cher</t>
+  </si>
+  <si>
+    <t>Côte-d'Or</t>
+  </si>
+  <si>
+    <t>Côtes-d'Armor</t>
+  </si>
+  <si>
+    <t>Creuse</t>
+  </si>
+  <si>
+    <t>Doubs</t>
+  </si>
+  <si>
+    <t>Eure</t>
+  </si>
+  <si>
+    <t>Eure-et-Loir</t>
+  </si>
+  <si>
+    <t>Finistère</t>
+  </si>
+  <si>
+    <t>Gers</t>
+  </si>
+  <si>
+    <t>Gironde</t>
+  </si>
+  <si>
+    <t>Hérault</t>
+  </si>
+  <si>
+    <t>Ille-et-Vilaine</t>
+  </si>
+  <si>
+    <t>Isère</t>
+  </si>
+  <si>
+    <t>Landes</t>
+  </si>
+  <si>
+    <t>Loir-et-Cher</t>
+  </si>
+  <si>
+    <t>Loire</t>
+  </si>
+  <si>
+    <t>Loire-Atlantique</t>
+  </si>
+  <si>
+    <t>Loiret</t>
+  </si>
+  <si>
+    <t>Lot</t>
+  </si>
+  <si>
+    <t>Lot-et-Garonne</t>
+  </si>
+  <si>
+    <t>Manche</t>
+  </si>
+  <si>
+    <t>Marne</t>
+  </si>
+  <si>
+    <t>Haute-Marne</t>
+  </si>
+  <si>
+    <t>Mayenne</t>
+  </si>
+  <si>
+    <t>Meurthe-et-Moselle</t>
+  </si>
+  <si>
+    <t>Meuse</t>
+  </si>
+  <si>
+    <t>Morbihan</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>Oise</t>
+  </si>
+  <si>
+    <t>Orne</t>
+  </si>
+  <si>
+    <t>Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>Pyrénées-Atlantiques</t>
+  </si>
+  <si>
+    <t>Hautes-Pyrénées</t>
+  </si>
+  <si>
+    <t>Pyrénées-Orientales</t>
+  </si>
+  <si>
+    <t>Haut-Rhin</t>
+  </si>
+  <si>
+    <t>Rhône</t>
+  </si>
+  <si>
+    <t>Haute-Saône</t>
+  </si>
+  <si>
+    <t>Saône-et-Loire</t>
+  </si>
+  <si>
+    <t>Sarthe</t>
+  </si>
+  <si>
+    <t>Savoie</t>
+  </si>
+  <si>
+    <t>Haute-Savoie</t>
+  </si>
+  <si>
+    <t>Seine-Maritime</t>
+  </si>
+  <si>
+    <t>Yvelines</t>
+  </si>
+  <si>
+    <t>Deux-Sèvres</t>
+  </si>
+  <si>
+    <t>Somme</t>
+  </si>
+  <si>
+    <t>Tarn</t>
+  </si>
+  <si>
+    <t>Var</t>
+  </si>
+  <si>
+    <t>Vendée</t>
+  </si>
+  <si>
+    <t>Vosges</t>
+  </si>
+  <si>
+    <t>Yonne</t>
+  </si>
+  <si>
+    <t>Territoire de Belfort</t>
+  </si>
+  <si>
+    <t>Essonne</t>
+  </si>
+  <si>
+    <t>Hauts-de-Seine</t>
+  </si>
+  <si>
+    <t>Seine-Saint-Denis</t>
+  </si>
+  <si>
+    <t>Val-d'Oise</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -158,6 +344,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -186,9 +383,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,407 +690,1088 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8490C60-CE07-4CD5-9861-10421FC1CA73}">
-  <dimension ref="A1:C37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BF2123-610B-4395-8ED3-FA697652A681}">
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="14" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" s="4">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30" s="4">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48" s="4">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49" s="4">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50" s="4">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53" s="4">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55" s="4">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56" s="4">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58" s="4">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" s="4">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61" s="4">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62" s="4">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63" s="4">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64" s="4">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66" s="4">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67" s="4">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68" s="4">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70" s="4">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71" s="4">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72" s="4">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74" s="4">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75" s="4">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76" s="4">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+      <c r="C77" s="4">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" s="4">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80" s="4">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81" s="4">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82" s="4">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83" s="4">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="4">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88" s="4">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" s="4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90" s="4">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92" s="4">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93" s="4">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94" s="4">
         <v>13.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="95" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95" s="4">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96" s="4">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97" s="4">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18">
-        <v>3</v>
-      </c>
-      <c r="C18">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>36.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
-      </c>
-      <c r="C26">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>16.100000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30">
-        <v>3</v>
-      </c>
-      <c r="C30">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>19.899999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" s="4">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3"/>
+      <c r="B99" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
